--- a/output/pdf_financials_xlsx/HAPB.xlsx
+++ b/output/pdf_financials_xlsx/HAPB.xlsx
@@ -3117,22 +3117,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.621825</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.702819</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.530652</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.392054</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.702863</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.682628</v>
       </c>
     </row>
     <row r="93">
@@ -5322,7 +5322,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HAPB.xlsx
+++ b/output/pdf_financials_xlsx/HAPB.xlsx
@@ -1468,25 +1468,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.879702</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.414952</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.630119</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.295221</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.212653</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.132274</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.081815</v>
       </c>
     </row>
     <row r="35">
@@ -1524,25 +1524,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.879702</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.414952</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.630119</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.295221</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.212653</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.132274</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.081815</v>
       </c>
     </row>
     <row r="37">
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.939365</v>
+        <v>0.059663</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.642613</v>
+        <v>0.227661</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.630119</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.295221</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.212653</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.513919</v>
+        <v>0.381645</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.232358</v>
+        <v>0.150543</v>
       </c>
     </row>
     <row r="49">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/HAPB.xlsx
+++ b/output/pdf_financials_xlsx/HAPB.xlsx
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.134624</v>
+        <v>0.211497</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.212121</v>
+        <v>0.212498</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.212498</v>
@@ -1332,10 +1332,10 @@
         <v>-0.401543</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.461487</v>
+        <v>-6.384614</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.499448</v>
+        <v>-2.499071</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.461536</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1057.739446729865</v>
+        <v>-1045.155407717102</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-259.2390379900182</v>
+        <v>-259.199936109394</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-368.4488056805349</v>
@@ -3324,22 +3324,22 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.134624</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.212121</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.212498</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.212498</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.211497</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.10405</v>
       </c>
     </row>
     <row r="101">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">

--- a/output/pdf_financials_xlsx/HAPB.xlsx
+++ b/output/pdf_financials_xlsx/HAPB.xlsx
@@ -2322,25 +2322,25 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.023062</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.387012</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.686103</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.844175</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.838663</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>1.488714</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.464647</v>
       </c>
     </row>
     <row r="65">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-10.335544</v>
+        <v>-6.596111</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-6.751972</v>
+        <v>-2.711569</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-3.322363</v>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.134624</v>
+        <v>0.211497</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.212121</v>
+        <v>0.212498</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0.212498</v>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0</v>
+        <v>-0.108581</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>-0.253767</v>
+        <v>0.10484</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0.022446</v>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>-0.167999</v>
+        <v>-0.381645</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0.227661</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.5445</v>
+        <v>0.732332</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.359112</v>
+        <v>0.531235</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.738959</v>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.376501</v>
+        <v>0.242106</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.333006</v>
+        <v>0.8637359999999999</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.761405</v>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>2.513183</v>
+        <v>0.270297</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>3.08051</v>
+        <v>0.045093</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.9285949999999999</v>
@@ -4179,7 +4179,7 @@
         <v>-0.075903</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>-0.089916</v>
+        <v>-0.019572</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>-0.135884</v>
@@ -4206,10 +4206,10 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>5.166899</v>
+        <v>4.211217</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>5.263868</v>
+        <v>2.02189</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>1.845977</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.879702</v>
+        <v>0.212653</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>3.414952</v>
+        <v>0.295221</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>3.630119</v>
@@ -4266,10 +4266,10 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>0.02952</v>
+        <v>-0.02349</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.045544</v>
+        <v>0.025521</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>-0.023856</v>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>2.53525</v>
+        <v>-0.08037900000000001</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.215167</v>
+        <v>-0.082568</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>-3.334898</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>3.414952</v>
+        <v>0.132274</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>3.630119</v>
+        <v>0.212653</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>0.295221</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.120551</v>
+        <v>-4.268106</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-5.074245</v>
+        <v>-2.129979</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-5.194399</v>
@@ -4415,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.134624</v>
+        <v>0.211497</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.212121</v>
+        <v>0.212498</v>
       </c>
       <c r="H76" s="5" t="n">
         <v>0.212498</v>
@@ -8148,10 +8148,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="5" t="n">
+        <v>0.449993</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -8199,10 +8197,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F78" s="5" t="n">
+        <v>0.390292</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -8253,10 +8249,10 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>2.513183</v>
+        <v>0.270297</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>3.08051</v>
+        <v>0.045093</v>
       </c>
       <c r="H79" s="5" t="n">
         <v>0.9285949999999999</v>
@@ -8396,10 +8392,10 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>3.347427</v>
+        <v>1.09086</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-2.391914</v>
+        <v>-0.208718</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>-3.471306</v>
@@ -8437,10 +8433,10 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-0.09216299999999999</v>
+        <v>-0.168756</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.000238</v>
+        <v>0.088129</v>
       </c>
       <c r="H83" s="5" t="n">
         <v>-0.078622</v>
@@ -8530,13 +8526,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" s="5" t="n">
+        <v>-0.108581</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.253767</v>
+        <v>0.10484</v>
       </c>
       <c r="H85" s="5" t="n">
         <v>0.022446</v>
@@ -8626,15 +8620,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="5" t="n">
+        <v>-0.070148</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.133912</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -8673,13 +8663,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F88" s="5" t="n">
+        <v>-0.08813600000000001</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.390961</v>
+        <v>-0.163381</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>-0.188244</v>
@@ -8721,10 +8709,10 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-2.120551</v>
+        <v>-4.268106</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-5.074245</v>
+        <v>-2.129979</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>-5.194399</v>
@@ -8862,10 +8850,10 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.555</v>
+        <v>4.05</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>4.761589</v>
+        <v>0.541885</v>
       </c>
       <c r="H92" s="5" t="n">
         <v>2.419093</v>
@@ -8954,12 +8942,10 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>4.651907</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.161217</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.499577</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -9005,10 +8991,10 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>5.166899</v>
+        <v>4.211217</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>5.263868</v>
+        <v>2.02189</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>1.845977</v>
@@ -9050,10 +9036,10 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.02952</v>
+        <v>-0.02349</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.045544</v>
+        <v>0.025521</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.023856</v>
@@ -9092,13 +9078,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>-0.08037900000000001</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.215167</v>
+        <v>-0.082568</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>-3.334898</v>
@@ -9140,10 +9124,10 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.879702</v>
+        <v>0.212653</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>3.414952</v>
+        <v>0.295221</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>3.630119</v>
@@ -9185,10 +9169,10 @@
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>3.414952</v>
+        <v>0.132274</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>3.630119</v>
+        <v>0.212653</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>0.295221</v>
@@ -9209,33 +9193,37 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>December 31, 2023 December</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="5" t="n">
+        <v>-6.596111</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-2.711569</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.002022</v>
+        <v>-3.322363</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-2.711569</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -9256,35 +9244,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Finders’ warrants</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-10.335544</v>
+        <v>0.152898</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-6.751972</v>
+        <v>-0.113362</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-3.322363</v>
+        <v>0.036713</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-2.711569</v>
+        <v>-0.113362</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -9305,33 +9289,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finders’ warrants</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Decrease / (increase) in prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.152898</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>0.036713</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>-0.113362</v>
+        <v>-0.381645</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.227661</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -9352,35 +9342,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Finders’ shares</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.157527</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.732332</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.531235</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.016443</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.738959</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0.531235</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -9406,34 +9396,28 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Decrease / (increase) in prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>(Decrease) / increase in product warranty liability</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>-0.167999</v>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.227661</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.048656</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-0.052805</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>-0.048656</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -9454,35 +9438,35 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Increase in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>License fees paid</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.5445</v>
+        <v>-0.697495</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.359112</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.738959</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>0.531235</v>
+        <v>-0.02</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -9503,15 +9487,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>(Decrease) / increase in product warranty liability</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Investing activities total</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9522,14 +9510,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="5" t="n">
-        <v>0.052805</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>-0.052805</v>
-      </c>
-      <c r="I106" s="5" t="n">
-        <v>-0.048656</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -9550,35 +9544,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>License fees paid</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>-0.697495</v>
+        <v>-0.075903</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.019572</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>-0.135884</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>-0.019572</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -9597,14 +9591,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cash acquired on amalgamation (note 6)</t>
+          <t>December 31, 2023 December</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -9613,23 +9603,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" s="5" t="n">
-        <v>0.47186</v>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -9650,12 +9638,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Exercise of warrants</t>
+          <t>Finders’ shares</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -9665,13 +9653,15 @@
         </is>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.035895</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>0.592195</v>
+        <v>0.157527</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-0.307957</v>
+        <v>0.016443</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -9697,12 +9687,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Warrant liability</t>
+          <t>Cash acquired on amalgamation (note 6)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -9711,18 +9701,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>0.47186</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="5" t="n">
-        <v>-0.129275</v>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9753,30 +9743,28 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.075903</v>
+        <v>0.035895</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-0.089916</v>
+        <v>0.592195</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>-0.135884</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>-0.019572</v>
+        <v>-0.307957</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -9797,12 +9785,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cash acquired on amalgamation</t>
+          <t>Warrant liability</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -9821,10 +9809,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>-0.129275</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -9850,12 +9836,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Share-based - Zander acquisition</t>
+          <t>Cash acquired on amalgamation</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -9864,8 +9850,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" s="5" t="n">
-        <v>1.466434</v>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -9901,12 +9889,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital balances</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Increase in inventory</t>
+          <t>Share-based - Zander acquisition</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -9916,10 +9904,12 @@
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.029829</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>-0.253767</v>
+        <v>1.466434</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -9955,7 +9945,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Increase in product warranty liability</t>
+          <t>Increase in inventory</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -9964,13 +9954,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="5" t="n">
+        <v>-0.029829</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.052805</v>
+        <v>-0.253767</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -10006,7 +9994,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Increase in unearned revenue</t>
+          <t>Increase in product warranty liability</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -10015,11 +10003,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>0.188391</v>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.390961</v>
+        <v>0.052805</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -10050,12 +10040,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital balances</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Increase in cash during the year</t>
+          <t>Increase in unearned revenue</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -10065,10 +10055,10 @@
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>2.53525</v>
+        <v>0.188391</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.215167</v>
+        <v>0.390961</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -10094,17 +10084,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>How the matter was addressed in the audit</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>I performed other analytical procedures to satisfy myself by alternative means concerning the cost of sales amount during the year ended December</t>
+          <t>Increase in cash during the year</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -10114,10 +10104,10 @@
         </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>2.53525</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.215167</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -10148,12 +10138,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Other Matter</t>
+          <t>How the matter was addressed in the audit</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Other Matter another auditor who expressed an unmodiﬁed opinion on those statements on April</t>
+          <t>I performed other analytical procedures to satisfy myself by alternative means concerning the cost of sales amount during the year ended December</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -10163,7 +10153,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>2.9e-05</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>0.002024</v>
@@ -10197,12 +10187,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Morton Garellek, CPA auditor</t>
+          <t>Other Matter</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Montréal (Québec), June</t>
+          <t>Other Matter another auditor who expressed an unmodiﬁed opinion on those statements on April</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -10212,10 +10202,10 @@
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>2.2e-05</v>
+        <v>2.9e-05</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.002025</v>
+        <v>0.002024</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -10246,29 +10236,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>Morton Garellek, CPA auditor</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Montréal (Québec), June</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.610877</v>
+        <v>2.2e-05</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.964148</v>
+        <v>0.002025</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -10304,20 +10290,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Royalties</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>-0.186311</v>
+        <v>0.610877</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>-0.14</v>
+        <v>0.964148</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -10353,30 +10343,30 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Royalties</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.232693</v>
+        <v>-0.186311</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.412125</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>0.8810519999999999</v>
-      </c>
-      <c r="I123" s="5" t="n">
-        <v>0.552125</v>
+        <v>-0.14</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -10402,12 +10392,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Cost of goods sold</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>GrossProfit</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10416,20 +10406,16 @@
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.191873</v>
+        <v>0.232693</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.412023</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.412125</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>0.8810519999999999</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>0.552125</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -10450,17 +10436,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets (note 5)</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10469,16 +10455,20 @@
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.211497</v>
+        <v>0.191873</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.212498</v>
-      </c>
-      <c r="H125" s="5" t="n">
-        <v>0.212498</v>
-      </c>
-      <c r="I125" s="5" t="n">
-        <v>0.212498</v>
+        <v>0.412023</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -10504,28 +10494,30 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Amortization of intangible assets (note 5)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>0.179732</v>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>2.219544</v>
+        <v>0.211497</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>1.872328</v>
+        <v>0.212498</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>3.935873</v>
+        <v>0.212498</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>1.872328</v>
+        <v>0.212498</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -10551,34 +10543,28 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>General and administrative (note 20)</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>0.179732</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>1.335579</v>
+        <v>2.219544</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.732835</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.872328</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>3.935873</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>1.872328</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -10604,26 +10590,34 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Product development costs</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>General and administrative (note 20)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.889456</v>
+        <v>1.335579</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.740714</v>
-      </c>
-      <c r="H128" s="5" t="n">
-        <v>0.196055</v>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>0.740714</v>
+        <v>0.732835</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -10649,28 +10643,26 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="n">
-        <v>0.077043</v>
+          <t>Product development costs</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.267704</v>
+        <v>0.889456</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.091267</v>
+        <v>0.740714</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.163282</v>
+        <v>0.196055</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>0.091267</v>
+        <v>0.740714</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -10696,30 +10688,28 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Salaries and wages</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>0.077043</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.053055</v>
+        <v>0.267704</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.066384</v>
+        <v>0.091267</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.37535</v>
+        <v>0.163282</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>0.066384</v>
+        <v>0.091267</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -10745,26 +10735,30 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Salaries and wages</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.270297</v>
+        <v>0.053055</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.045093</v>
+        <v>0.066384</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0.9285949999999999</v>
+        <v>0.37535</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>0.045093</v>
+        <v>0.066384</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -10790,28 +10784,26 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="n">
-        <v>0.401543</v>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>5.247132</v>
+        <v>0.270297</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>3.761119</v>
+        <v>0.045093</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>7.743822</v>
+        <v>0.9285949999999999</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>3.761119</v>
+        <v>0.045093</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -10837,24 +10829,28 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Operating loss before other item</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E133" s="5" t="n">
-        <v>-0.401543</v>
+        <v>0.401543</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>-5.055259</v>
+        <v>5.247132</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>-3.349096</v>
+        <v>3.761119</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>-6.793669</v>
+        <v>7.743822</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>-3.349096</v>
+        <v>3.761119</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -10875,35 +10871,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant liability (note 13)</t>
+          <t>Operating loss before other item</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="5" t="n">
+        <v>-0.401543</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-1.090859</v>
+        <v>-5.055259</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.637527</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.349096</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>-6.793669</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>-3.349096</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -10929,7 +10919,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Impairment expense</t>
+          <t>Change in fair value of warrant liability (note 13)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10939,12 +10929,10 @@
         </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>-0.449993</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.090859</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.637527</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10980,24 +10968,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment expense</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-6.596111</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>-2.711569</v>
+        <v>-0.449993</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -11033,24 +11019,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F137" s="5" t="n">
+        <v>-6.596111</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-2.711569</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -11086,24 +11072,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F138" s="5" t="n">
-        <v>-6.596111</v>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>-2.711569</v>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -11139,12 +11125,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Loss per share– basic and diluted (note 14)</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11153,10 +11139,10 @@
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-6.596111</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-2.711569</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -11187,31 +11173,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares outstanding - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Loss per share– basic and diluted (note 14)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>160.481929</v>
+        <v>-4e-08</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>104.415648</v>
-      </c>
-      <c r="H140" s="5" t="n">
-        <v>76.63043999999999</v>
-      </c>
-      <c r="I140" s="5" t="n">
-        <v>104.415648</v>
+        <v>-3e-08</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -11232,12 +11226,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>For the years-ended December 31, 2023 and 2022</t>
+          <t>Weighted-average number of shares</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>December 31, 2023 December</t>
+          <t>Weighted-average number of shares outstanding - basic and diluted</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -11246,21 +11240,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" s="5" t="n">
+        <v>160.481929</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>104.415648</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0.002022</v>
+        <v>76.63043999999999</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>104.415648</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -11281,12 +11271,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Revenues</t>
+          <t>For the years-ended December 31, 2023 and 2022</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sales on products</t>
+          <t>December 31, 2023 December</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -11295,17 +11285,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>0.661882</v>
-      </c>
-      <c r="G142" s="5" t="n">
-        <v>1.72853</v>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H142" s="5" t="n">
-        <v>1.820541</v>
+        <v>0.002022</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>0.951662</v>
+        <v>3.1e-05</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -11331,30 +11325,26 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Revenues total</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Sales on products</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.145238</v>
+        <v>0.661882</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.479289</v>
+        <v>1.72853</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.939489</v>
+        <v>1.820541</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0.399537</v>
+        <v>0.951662</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -11375,33 +11365,35 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Revenues</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Shipping income</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>Revenues total</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F144" s="5" t="n">
+        <v>0.145238</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.011172</v>
+        <v>0.479289</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.010664</v>
+        <v>0.939489</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.012486</v>
+        <v>0.399537</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -11422,35 +11414,33 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other revenue</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>General and administrative (note 18)</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="n">
-        <v>0.144768</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>0.821542</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shipping income</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.011172</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>1.754093</v>
+        <v>0.010664</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>0.732835</v>
+        <v>0.012486</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -11476,17 +11466,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Royalty fees</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>General and administrative (note 18)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>0.144768</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.113362</v>
+        <v>0.821542</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -11494,12 +11486,10 @@
         </is>
       </c>
       <c r="H146" s="5" t="n">
-        <v>0.178076</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.754093</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.732835</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -11520,12 +11510,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant liability (note 15)</t>
+          <t>Royalty fees</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -11535,16 +11525,20 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-3.347427</v>
-      </c>
-      <c r="G147" s="5" t="n">
-        <v>2.391914</v>
+        <v>0.113362</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H147" s="5" t="n">
-        <v>3.119635</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>0.637527</v>
+        <v>0.178076</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -11570,28 +11564,26 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>-0.401543</v>
+          <t>Change in fair value of warrant liability (note 15)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-10.335544</v>
+        <v>-3.347427</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>-6.751972</v>
+        <v>2.391914</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>-3.674034</v>
+        <v>3.119635</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>-2.711569</v>
+        <v>0.637527</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -11617,30 +11609,28 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>-0.401543</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.02952</v>
+        <v>-10.335544</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.003651</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.751972</v>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>-3.674034</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-2.711569</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -11666,28 +11656,30 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>-0.401543</v>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-10.306024</v>
+        <v>0.02952</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-6.748321</v>
-      </c>
-      <c r="H150" s="5" t="n">
-        <v>-3.674034</v>
-      </c>
-      <c r="I150" s="5" t="n">
-        <v>-2.711569</v>
+        <v>0.003651</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -11713,30 +11705,28 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Loss per share– basic and diluted (note 14)</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>-0.401543</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>-2.3e-07</v>
+        <v>-10.306024</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>-6.748321</v>
       </c>
       <c r="H151" s="5" t="n">
-        <v>-9e-08</v>
+        <v>-3.674034</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-2.711569</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -11757,17 +11747,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>General and administrative (note 19)</t>
+          <t>Loss per share– basic and diluted (note 14)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11775,21 +11765,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" s="5" t="n">
+        <v>-2.3e-07</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>2.349169</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>1.754093</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-08</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -11815,27 +11801,29 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Interest accretion and expense on convertible debentures</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>General and administrative (note 19)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F153" s="5" t="n">
-        <v>0.168621</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>2.349169</v>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>1.754093</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -11866,7 +11854,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 11)</t>
+          <t>Interest accretion and expense on convertible debentures</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -11875,16 +11863,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>3.08051</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>0.9285949999999999</v>
+      <c r="F154" s="5" t="n">
+        <v>0.168621</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -11910,12 +11900,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant liability (note 14)</t>
+          <t>Share-based compensation (note 11)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -11930,10 +11920,10 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>2.391914</v>
+        <v>3.08051</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>3.119635</v>
+        <v>0.9285949999999999</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -11964,14 +11954,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss per share– basic and diluted (note 13)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Change in fair value of warrant liability (note 14)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -11983,10 +11969,10 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>-1.3e-07</v>
+        <v>2.391914</v>
       </c>
       <c r="H156" s="5" t="n">
-        <v>-5e-08</v>
+        <v>3.119635</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -12012,26 +11998,34 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Weighted-average number of shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>46.661095</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>45.356219</v>
+          <t>Loss per share– basic and diluted (note 13)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>50.722011</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="H157" s="5" t="n">
-        <v>76.63043999999999</v>
+        <v>-5e-08</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -12057,30 +12051,26 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted-average number of shares</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 12)</t>
+          <t>Weighted-average number of shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E158" s="5" t="n">
+        <v>46.661095</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>2.513183</v>
+        <v>45.356219</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>3.08051</v>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50.722011</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>76.63043999999999</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -12111,7 +12101,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Share-based compensation - Zander acquisition (note 6)</t>
+          <t>Share-based compensation (note 12)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -12121,12 +12111,10 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>1.466434</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.513183</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>3.08051</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12162,21 +12150,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Amortization of intangible assets</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Share-based compensation - Zander acquisition (note 6)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.134624</v>
+        <v>1.466434</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -12217,17 +12201,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 10)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Amortization of intangible assets</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F161" s="5" t="n">
-        <v>2.513183</v>
+        <v>0.134624</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -12268,7 +12256,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Share-based - Zander acquisition (note 6)</t>
+          <t>Share-based compensation (note 10)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -12278,7 +12266,7 @@
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>1.466434</v>
+        <v>2.513183</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -12314,12 +12302,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Change in fair value of warrants liability (note 13)</t>
+          <t>Share-based - Zander acquisition (note 6)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12329,7 +12317,7 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>-3.347427</v>
+        <v>1.466434</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -12370,41 +12358,92 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
+          <t>Change in fair value of warrants liability (note 13)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>-3.347427</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
           <t>Loss per share– basic and diluted (note 12)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n">
+      <c r="E165" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F165" s="5" t="n">
         <v>-2.3e-07</v>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>-</t>
         </is>
